--- a/Milestone/API docs/MorningBriefingAI_API_Design.xlsx
+++ b/Milestone/API docs/MorningBriefingAI_API_Design.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="167">
   <si>
     <t>Status</t>
   </si>
@@ -50,33 +50,40 @@
   </si>
   <si>
     <t>{
-  lat: number,   // rounded to 0.1 client-side
-  lon: number
+  lat?: number,       // latitude (default 37.5665); rounded to 0.1 client-side
+  lon?: number,       // longitude (default 126.978)
+  city?: string,      // overrides lat/lon when provided
+  lang?: "ko" | "en"  // default "en"
 }</t>
   </si>
   <si>
     <t>{
   temp: number,
   feels_like: number,
-  humidity: number,    // 0-100
-  condition: string,   // e.g. "Clear"
-  icon: string,        // OWM icon code
+  humidity: number,           // 0-100
+  condition: string,          // e.g. "light rain"
+  conditionId: number | null, // OWM condition id for icon logic
+  icon: string,               // OWM icon code e.g. "10d"
   city: string,
-  precipitation: number,  // mm
-  airQuality: string   // "Good"|"Moderate"|"Bad"|"Very Bad"
+  precipitation: number,      // 0-100 probability (from cloud cover + rain/snow)
+  airQualityIndex: number     // raw AQI 1-5 (mapping done client-side)
 }</t>
   </si>
   <si>
     <t>useDataStore.fetchWeather()
 -&gt; Edge Function weather/index.ts
 -&gt; OpenWeatherMap current weather API
--&gt; OpenWeatherMap Air Pollution API (parallel)</t>
+   + Air Pollution API (parallel)
+-&gt; When lang=ko: also calls OWM Geocoding reverse API
+   for Korean city name</t>
   </si>
   <si>
     <t>Auth: no auth required (secrets server-side).
 Coordinates rounded to 0.1 precision client-side for cache reuse.
-AQI mapping: 1=Good, 2-3=Moderate, 4=Bad, 5=Very Bad.
-Timeout: 25s. Cache key: weather_{rLat}_{rLon} (6h TTL)</t>
+AQI mapping (1-5) done client-side in useDataStore:
+  1=Good, 2-3=Moderate, 4=Bad, 5=Very Bad.
+precipitation: 0-100 probability, not raw mm.
+Timeout: 25s. Cache key: weather_{rLat}_{rLon} (6h TTL).</t>
   </si>
   <si>
     <t>Fetch Stocks</t>
@@ -94,25 +101,31 @@
   {
     symbol: string,
     price: number,
-    change: number,        // absolute
-    changePercent: number  // percent
-    type: string
-    currency: string
+    change: number,          // absolute change
+    changePercent: string,   // e.g. "+1.23%" or "-0.50%"
+    type: string,            // "index"|"stock"|"etf"|"currency"|"commodity"|"unknown"
+    currency: string,        // ISO code e.g. "USD", "KRW"
+    error?: string           // present on failed symbols; row still included
   }, ...
 ]</t>
   </si>
   <si>
     <t>useDataStore.fetchStocks({symbols})
 -&gt; Edge Function stocks/index.ts
--&gt; Yahoo Finance (primary). Strict validation: price &gt; 0 required. type and currency metadata auto-detected from Yahoo response.</t>
+-&gt; TwelveData (primary, for currencies + individual tickers)
+   requires TWELVEDATA_API_KEY — HTTP 500 if unset
+-&gt; Yahoo Finance v8 chart API
+   (for indices/commodities defined in YAHOO_SYMBOL_MAP)</t>
   </si>
   <si>
     <t>Auth: no auth required.
-Symbols normalized to uppercase. 8 fixed index symbols:
-SP500-&gt;^GSPC, KOSPI-&gt;^KS11, NASDAQ-&gt;^IXIC, USDKRW-&gt;KRW=X,
-VIX-&gt;^VIX, CRUDE-&gt;CL=F, DXY-&gt;DX=F, DJI-&gt;^DJI.
-User-added tickers validated strictly (price &gt; 0); invalid tickers rejected.
-⚠ Edge Function changes require manual redeploy via Supabase Dashboard.</t>
+Symbols normalized to uppercase.
+Yahoo symbol map (indices/commodities):
+  SP500-&gt;^GSPC, KOSPI-&gt;^KS11, NASDAQ-&gt;^IXIC,
+  VIX-&gt;^VIX, DJI-&gt;^DJI, DXY-&gt;DX-Y.NYB, CRUDE-&gt;CL=F.
+TwelveData: USDKRW-&gt;USD/KRW, all stock/ETF tickers.
+Failed/zero-price symbols: zero-value row + error field (not removed).
+Edge Function changes require manual redeploy via Supabase Dashboard.</t>
   </si>
   <si>
     <t>Fetch Trends</t>
@@ -124,25 +137,25 @@
     <t>{
   mode: "trends",
   query: string,
-  max_results?: number,       // default 8
+  max_results?: number,           // default 8
   include_domains?: string[],
+  exclude_domains?: string[],     // NEW
   time_range?: string
 }</t>
   </si>
   <si>
     <t>{
   answer: string | null,
-  results: [
+  results: [                      // no image field in trends mode
     {
       title: string,
       url: string,
       content: string,
       published_date: string | null,
-      score: number | null,
-      image: string | null
+      score: number | null
     }, ...
   ],
-  trends: string[]  // article titles for fallback display
+  trends: string[]  // cleaned+deduped titles (max 8)
 }</t>
   </si>
   <si>
@@ -163,10 +176,11 @@
   <si>
     <t>{
   mode: "news",
-  query: string,              // includes top-5 interest keywords
-  max_results?: number,       // default 10
+  query: string,                  // includes top-5 interest keywords
+  max_results?: number,           // default 10
   location?: { lat: number, lon: number },
-  include_domains?: string[]
+  include_domains?: string[],
+  exclude_domains?: string[]
 }</t>
   </si>
   <si>
@@ -202,38 +216,50 @@
     <t>Tavily Generic Search</t>
   </si>
   <si>
-    <t>{
+    <t>// Single query:
+{
   mode: "search",
   query: string,
   max_results?: number,
   include_domains?: string[],
-  search_topic?: string,  // default "general"
+  exclude_domains?: string[],
+  search_topic?: string,     // default "general"
   time_range?: string
+}
+// Batch:
+{
+  queries: Array&lt;{
+    mode?: string, query: string,
+    max_results?: number,
+    include_domains?: string[],
+    exclude_domains?: string[],
+    search_topic?: string,
+    time_range?: string
+  }&gt;
 }</t>
   </si>
   <si>
-    <t>{
+    <t>// Single: same shape as mode=news
+{
   answer: string | null,
-  results: [
-    {
-      title: string,
-      url: string,
-      content: string,
-      published_date: string | null,
-      image: string | null,
-      score: number | null
-    }, ...
-  ]
-}</t>
+  results: [{ title, url, content,
+    published_date, image, score }]
+}
+// Batch:
+{ batch: Array&lt;/* single output shape,
+  or {error,results:[],answer:null}
+  on per-query failure */&gt; }</t>
   </si>
   <si>
-    <t>Used internally by aiService.js and smart-widget Edge Function for keyword-specific Tavily searches (shopping, brand pages, restaurant data, etc.)</t>
+    <t>Used by aiService.ts and smart-widget Edge Function
+for keyword-specific Tavily searches.
+Batch mode: all queries run in parallel server-side.</t>
   </si>
   <si>
     <t>Auth: no auth required.
 Same Tavily endpoint as news/trends, parameterized by mode.
 search_topic defaults to "general" (vs "news" for mode=news).
-NEW — not in original template.</t>
+Batch: send { queries: [...] } -&gt; returns { batch: [...] }.</t>
   </si>
   <si>
     <t>Generate Groq Completion</t>
@@ -277,23 +303,57 @@
   </si>
   <si>
     <t>{
-  token: string,  // Google OAuth provider_token
-  action?: "list"|"read"|"create"|"update"|"delete",
+  token: string,         // Google OAuth provider_token
+  action?: "list"|"read"|"create"|"update"|"delete",  // default "list"
   // list:
-  timeMin?: string, timeMax?: string,
-  todayOnly?: boolean, date?: string,
+  timeMin?: string,      // ISO datetime (takes priority over date/todayOnly)
+  timeMax?: string,
+  todayOnly?: boolean,
+  date?: string,         // YYYY-MM-DD (required for create/update)
   // create/update:
-  title?: string, startTime?: string, endTime?: string,
-  location?: string, description?: string,
+  startTime?: string,    // HH:MM 24-hour; omit for all-day
+  endTime?: string,      // HH:MM; auto-set to startTime+1h if &lt;=startTime
+  timeZone?: string,
+  allDay?: boolean,
+  title?: string,
+  location?: string,
+  description?: string,
+  attendees?: Array&lt;string | { email, displayName?, optional?, responseStatus? }&gt;,
+  visibility?: "default"|"public"|"private"|"confidential",
+  availability?: "busy"|"free",
+  remindersUseDefault?: boolean,
+  reminderOverrides?: Array&lt;{ method: "popup"|"email", minutes: number }&gt;,
+  addGoogleMeet?: boolean,
+  clearConference?: boolean,
+  recurrence?: string[],
+  sendUpdates?: boolean,
   // read/update/delete:
   eventId?: string
 }</t>
   </si>
   <si>
-    <t>// list -&gt; array of events:
-[{ id, summary, start, end, location, description, attendees }]
-// create/update -&gt; single event object
-// delete -&gt; { success: true }</t>
+    <t>// list -&gt; array; create|update|read -&gt; single object:
+{
+  id: string,
+  title: string,
+  start: string,          // ISO or YYYY-MM-DD (all-day)
+  end: string,
+  allDay: boolean,
+  location: string | null,
+  description: string | null,
+  attendees: Array&lt;{ email, displayName, responseStatus, optional }&gt;,
+  visibility: string,
+  availability: string,   // "busy"|"free"
+  meetLink: string | null,
+  addGoogleMeet: boolean,
+  conferenceStatus: string | null,
+  remindersUseDefault: boolean,
+  reminderOverrides: Array&lt;{ method, minutes }&gt;,
+  recurrence: string[],
+  recurringEventId: string | null,
+  originalStartTime: string | null
+}
+// delete -&gt; { success: true, id: string }</t>
   </si>
   <si>
     <t>useGoogleCalendarStore.fetchEvents()
@@ -304,10 +364,10 @@
   </si>
   <si>
     <t>Auth: Supabase JWT + Google OAuth provider token.
-Required Google OAuth scope: https://www.googleapis.com/auth/calendar
+Required scope: https://www.googleapis.com/auth/calendar
 Single endpoint multiplexed by action param.
-todayOnly: true uses timeMin: now.toISOString() (excludes past).
-JWT validated server-side via supabase.auth.getUser(jwt) → 401 on failure.
+date (YYYY-MM-DD) required for create/update.
+startTime/endTime are HH:MM strings (not ISO datetime).
 Timeout: 25s.</t>
   </si>
   <si>
@@ -318,21 +378,46 @@
   </si>
   <si>
     <t>{
-  token: string,  // Google OAuth provider_token
-  action?: "list"|"create"|"update"|"delete"|"move"|"clearCompleted",
-  taskListId?: string,  // default "@default"
+  token: string,             // Google OAuth provider_token
+  action?: "list"|"create"|"update"|"delete"|"move"|"clearCompleted"
+         | "listTaskLists"|"createTaskList",   // default "list"
+  taskListId?: string,       // default "@default"
   taskId?: string,
-  title?: string, notes?: string, due?: string,
+  title?: string,
+  notes?: string,
+  due?: string,              // ISO datetime
+  status?: "needsAction"|"completed",
   completed?: boolean,
   // move:
-  previousId?: string, parentId?: string
+  sourceTaskListId?: string,
+  destinationTaskListId?: string,
+  // list:
+  allTaskLists?: boolean,    // fetch + merge all task lists
+  showCompleted?: boolean,   // default true
+  showHidden?: boolean       // default true
 }</t>
   </si>
   <si>
     <t>// list -&gt; array:
-[{ id, title, notes, due, status, completed, taskListId }]
-// create/update/move -&gt; single task object
-// delete/clearCompleted -&gt; { success: true }</t>
+[
+  {
+    id: string,
+    title: string,
+    notes: string,
+    due: string | null,
+    status: "needsAction"|"completed",
+    completed: boolean,
+    completedAt: string | null,
+    updated: string | null,
+    hidden: boolean,
+    deleted: boolean,
+    taskListId: string
+  }, ...
+]
+// create|update|move -&gt; single task object
+// delete|clearCompleted -&gt; { success: true, id?: string }
+// listTaskLists -&gt; [{ id, title, updated }]
+// createTaskList -&gt; { id, title, updated }</t>
   </si>
   <si>
     <t>useGoogleCalendarStore.fetchTasks()
@@ -343,9 +428,10 @@
   </si>
   <si>
     <t>Auth: Supabase JWT + Google OAuth provider token.
-Required Google OAuth scope: https://www.googleapis.com/auth/tasks
-Single endpoint multiplexed by action.
-⚠ CORRECTION: Legacy [MB_META]...[/MB_META] in notes is stripped on read but no longer written (DOCS.md §5.8).
+Required scope: https://www.googleapis.com/auth/tasks
+move: between task lists (not reordering within list).
+Legacy [MB_META]...[/MB_META] in notes: stripped on read,
+  no longer written (per DOCS.md §5.8).
 Timeout: 25s.</t>
   </si>
   <si>
@@ -376,9 +462,11 @@
   <si>
     <t>Auth: Supabase JWT + Google OAuth provider token.
 Required scope: https://www.googleapis.com/auth/fitness.activity.read
-(Restricted scope — annual CASA review required.)
-Aggregated in 86400s bucket (1 day).
-Returns zeros on 403 (graceful fallback). Timeout: 25s.</t>
+  (Restricted scope — annual CASA Tier 2 review required.)
+Aggregated in 86400s bucket (1 day, midnight to now).
+On Google Fit error (e.g. 403 scope missing): Edge Function throws
+  with upstream HTTP status. Zeros fallback applied client-side
+  in useDataStore. Timeout: 25s.</t>
   </si>
   <si>
     <t>Smart Widget Query</t>
@@ -426,6 +514,38 @@
 Cache key: ${keyword}_${lang} (client-side in useWidgetStore).</t>
   </si>
   <si>
+    <t>Refresh Google Token</t>
+  </si>
+  <si>
+    <t>supabase.co/functions/v1/google-refresh</t>
+  </si>
+  <si>
+    <t>{
+  refresh_token: string   // Google OAuth refresh token
+}</t>
+  </si>
+  <si>
+    <t>{
+  access_token: string,
+  expires_in: number      // seconds until expiry (typically 3600)
+}</t>
+  </si>
+  <si>
+    <t>useAuthStore.ensureProviderToken() 4-step chain:
+1. Memory cache (get().providerToken)
+2. supabase.auth.getSession() -&gt; check provider_token
+3. supabase.auth.refreshSession() -&gt; check refreshed provider_token
+4. This endpoint -&gt; calls Google oauth2.googleapis.com/token
+   server-side with GOOGLE_CLIENT_ID + GOOGLE_CLIENT_SECRET env vars.</t>
+  </si>
+  <si>
+    <t>Auth: no auth required (secrets held server-side).
+Secrets: GOOGLE_CLIENT_ID + GOOGLE_CLIENT_SECRET never exposed to client.
+Returns HTTP 401 if Google rejects refresh token (revoked/expired).
+Returns HTTP 500 if env vars not set.
+NEW — not in original template.</t>
+  </si>
+  <si>
     <t>GET</t>
   </si>
   <si>
@@ -436,31 +556,61 @@
 ?id=eq.u:{userId}:{cacheKey}</t>
   </si>
   <si>
-    <t>Query params:
-id = "u:{userId}:{cacheKey}"
-  e.g. "u:abc-123:weather_37.5_126.9"</t>
+    <t>{
+  keyword: string,         // user-defined widget keyword (required)
+  persona?: {              // nested object, all fields optional
+    persona?: string,      // persona slug from user_settings
+    age?: number | string,
+    job?: string,
+    interests?: string[]   // top fixed + dynamic interest keywords
+  },
+  token?: string,          // optional Google OAuth token
+  lat?: number,            // default 37.5665
+  lon?: number             // default 126.978
+}</t>
   </si>
   <si>
-    <t>[
-  {
-    id: string,
-    data: object,
-    fetched_at: string  // ISO timestamp
+    <t>{
+  keyword: string,
+  emoji: string,
+  lastUpdated: string,     // always "방금 전"
+  sections: Array&lt;
+    | { type: "summary", title: string, bullets: string[] }  // 3 bullets
+    | { type: "trend",   title: string, tags: string[] }     // 3-6 tags
+    | { type: "news",    title: string,
+        items: Array&lt;{ title, source, time, url }&gt; }         // max 6
+    | { type: "price",   title: string,
+        items: Array&lt;{ name, source, price, change }&gt; }
+  &gt;,
+  debug: {
+    step0: { route: string, reason: string },
+    step1?: { personaSummary, points, tags },
+    pipeline: "step0-routed"|"step1-step2-search"
   }
-]</t>
+}</t>
   </si>
   <si>
-    <t>useDataStore.readApiCache()
--&gt; Supabase REST SELECT
--&gt; Check 6h TTL against fetched_at
--&gt; CACHE HIT  -&gt; set state and return
--&gt; CACHE MISS -&gt; proceed to real API call</t>
+    <t>useWidgetStore.loadSmartWidget()
+-&gt; Edge Function smart-widget/index.ts
+-&gt; Step 0: Groq route classification (temp 0.3, JSON mode)
+   7 routes: weather|stocks|calendar|fitness|trends|restaurants|none
+   - route != none: call matching internal API -&gt; Groq formats sections
+     returns pipeline: "step0-routed"
+   - route = none: fall through to Step 1
+-&gt; Step 1: Groq generates 2 persona-tailored search points
+-&gt; Step 2: 2 parallel Tavily searches + Groq formats sections
+   returns pipeline: "step1-step2-search"</t>
   </si>
   <si>
-    <t>Auth: Supabase JWT (RLS). Users can only access their own rows.
-Key format: u:{userId}:{cacheKey}.
-TTL: 360 min / 6h (enforced app-side, not DB). Extended from 60 min on 2026-05-23 (commit 86a34a8) to cut Tavily token consumption.
-Cache keys are language-aware: news_{lang}_{interestFingerprint}, trends_full_{lang}, ${keyword}_${lang}.</t>
+    <t>Auth: Supabase JWT required.
+CORRECTION: Input was {lat,lon,userInput}, then {keyword,persona,age,job,...}.
+  Actual: persona is a nested object; no language field.
+CORRECTION: Output was {category,sections[summary/news/blog/video]}.
+  Actual: {keyword,emoji,lastUpdated,sections,debug}.
+  Section types: summary/trend/news/price.
+7 routable types (not "17 categories").
+Groq response_format: {type:"json_object"} enforced at every step.
+No server-side caching; client-side key: ${keyword} in useWidgetStore.</t>
   </si>
   <si>
     <t>Write API Cache (UPSERT)</t>
@@ -658,15 +808,19 @@
     <t>supabase.co/rest/v1/diaries</t>
   </si>
   <si>
-    <t>Row shape:
+    <t>// Current write columns:
 {
   user_id: uuid,
-  date: date,         // UNIQUE with user_id
-  diary_text: string,
-  memo: string,
-  answers: jsonb,     // [{question, answer}]
-  updated_at: timestamptz  // auto by trigger
-}</t>
+  date: date,                    // UNIQUE with user_id
+  ai_generated_diary: text,      // AI-generated draft
+  edited_diary: text,            // user-edited version
+  memo: text,
+  created_at: timestamptz,
+  updated_at: timestamptz        // auto-updated by trigger
+}
+// Legacy read-only columns (exist in DB, not written by current client):
+//   diary_text: text
+//   answers: jsonb  [{question, answer}]</t>
   </si>
   <si>
     <t>GET -&gt; array of diary rows
@@ -682,10 +836,10 @@
   <si>
     <t>Auth: Supabase JWT (RLS).
 UPSERT key: (user_id, date). updated_at auto-updated by DB trigger.
+Code inconsistency: useDiaryStore writes to ai_generated_diary/edited_diary
+  but reads from legacy diary_text/answers (useDiaryStore.ts:695).
+  Both column sets exist in live DB. New rows: diary_text = null.
 NEW — not in original template.</t>
-  </si>
-  <si>
-    <t>GET/POST</t>
   </si>
   <si>
     <t>Manage Q&amp;A</t>
@@ -694,12 +848,14 @@
     <t>supabase.co/rest/v1/user_qa</t>
   </si>
   <si>
-    <t>Row shape:
+    <t>// Row shape:
 {
+  id: uuid,
   user_id: uuid,
   question: string,
   answer: string,
-  asked_date: date
+  asked_date: date,
+  created_at: timestamptz
 }
 Indexed on (user_id, asked_date)</t>
   </si>
@@ -715,6 +871,9 @@
     <t>Auth: Supabase JWT (RLS).
 Index on (user_id, asked_date) for date-range queries.
 NEW — not in original template.</t>
+  </si>
+  <si>
+    <t>GET/POST</t>
   </si>
   <si>
     <t>Manage Briefing Snapshots</t>
@@ -878,7 +1037,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -889,11 +1048,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <color theme="1"/>
@@ -920,6 +1074,10 @@
       <name val="Courier New"/>
     </font>
     <font>
+      <color rgb="FF212121"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="9.0"/>
       <color rgb="FF1B5E20"/>
       <name val="Courier New"/>
@@ -931,6 +1089,11 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF212121"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF1B5E20"/>
       <name val="Arial"/>
     </font>
@@ -938,6 +1101,11 @@
       <b/>
       <color rgb="FF4527A0"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1004,7 +1172,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1014,52 +1182,13 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1071,10 +1200,13 @@
     <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1083,7 +1215,28 @@
     <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1092,11 +1245,32 @@
     <xf borderId="1" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1386,13 +1560,13 @@
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="2"/>
@@ -1415,28 +1589,28 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="2"/>
@@ -1474,13 +1648,13 @@
       <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="2"/>
@@ -1503,28 +1677,28 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="16" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="2"/>
@@ -1553,22 +1727,22 @@
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="9" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="2"/>
@@ -1591,28 +1765,28 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="23" t="s">
         <v>43</v>
       </c>
       <c r="I7" s="2"/>
@@ -1650,13 +1824,13 @@
       <c r="E8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>49</v>
       </c>
       <c r="I8" s="2"/>
@@ -1679,28 +1853,28 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>55</v>
       </c>
       <c r="I9" s="2"/>
@@ -1738,13 +1912,13 @@
       <c r="E10" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>61</v>
       </c>
       <c r="I10" s="2"/>
@@ -1767,28 +1941,28 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="25" t="s">
         <v>67</v>
       </c>
       <c r="I11" s="2"/>
@@ -1811,29 +1985,29 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1855,28 +2029,28 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>9</v>
+      <c r="B13" s="28" t="s">
+        <v>74</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="8" t="s">
         <v>80</v>
       </c>
       <c r="I13" s="2"/>
@@ -1899,28 +2073,28 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>68</v>
+      <c r="B14" s="4" t="s">
+        <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="25" t="s">
         <v>86</v>
       </c>
       <c r="I14" s="2"/>
@@ -1943,29 +2117,29 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
+      <c r="B15" s="28" t="s">
+        <v>74</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="18" t="s">
+      <c r="F15" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="G15" s="30" t="s">
         <v>91</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -1987,29 +2161,29 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="29" t="s">
-        <v>68</v>
+      <c r="B16" s="4" t="s">
+        <v>9</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="D16" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="E16" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="F16" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>96</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>97</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2031,29 +2205,29 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
+      <c r="B17" s="28" t="s">
+        <v>74</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="18" t="s">
+      <c r="D17" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="E17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="29" t="s">
         <v>100</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2075,29 +2249,29 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>101</v>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="25" t="s">
         <v>106</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2119,29 +2293,29 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="D19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="F19" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="G19" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="H19" s="30" t="s">
         <v>113</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>114</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2163,29 +2337,29 @@
       <c r="Z19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="25" t="s">
         <v>120</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -2207,29 +2381,29 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="E21" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="F21" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="G21" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="H21" s="8" t="s">
         <v>127</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>128</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -2251,29 +2425,29 @@
       <c r="Z21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="30" t="s">
-        <v>122</v>
+      <c r="B22" s="31" t="s">
+        <v>114</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="E22" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="16" t="s">
         <v>133</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -2295,29 +2469,29 @@
       <c r="Z22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="D23" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="E23" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="F23" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="G23" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="H23" s="30" t="s">
         <v>140</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>141</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -2339,29 +2513,29 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -2383,28 +2557,28 @@
       <c r="Z24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="30" t="s">
-        <v>142</v>
+      <c r="B25" s="31" t="s">
+        <v>148</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="30" t="s">
         <v>154</v>
       </c>
       <c r="I25" s="2"/>
@@ -2427,28 +2601,28 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="30" t="s">
-        <v>142</v>
+      <c r="B26" s="31" t="s">
+        <v>148</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="25" t="s">
         <v>160</v>
       </c>
       <c r="I26" s="2"/>
@@ -2471,14 +2645,30 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="A27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>166</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -29743,32 +29933,32 @@
       <c r="Z1000" s="2"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="2"/>
-      <c r="B1001" s="2"/>
-      <c r="C1001" s="2"/>
-      <c r="D1001" s="2"/>
-      <c r="E1001" s="2"/>
-      <c r="F1001" s="2"/>
-      <c r="G1001" s="2"/>
-      <c r="H1001" s="2"/>
-      <c r="I1001" s="2"/>
-      <c r="J1001" s="2"/>
-      <c r="K1001" s="2"/>
-      <c r="L1001" s="2"/>
-      <c r="M1001" s="2"/>
-      <c r="N1001" s="2"/>
-      <c r="O1001" s="2"/>
-      <c r="P1001" s="2"/>
-      <c r="Q1001" s="2"/>
-      <c r="R1001" s="2"/>
-      <c r="S1001" s="2"/>
-      <c r="T1001" s="2"/>
-      <c r="U1001" s="2"/>
-      <c r="V1001" s="2"/>
-      <c r="W1001" s="2"/>
-      <c r="X1001" s="2"/>
-      <c r="Y1001" s="2"/>
-      <c r="Z1001" s="2"/>
+      <c r="A1001" s="32"/>
+      <c r="B1001" s="32"/>
+      <c r="C1001" s="32"/>
+      <c r="D1001" s="32"/>
+      <c r="E1001" s="32"/>
+      <c r="F1001" s="32"/>
+      <c r="G1001" s="32"/>
+      <c r="H1001" s="32"/>
+      <c r="I1001" s="32"/>
+      <c r="J1001" s="32"/>
+      <c r="K1001" s="32"/>
+      <c r="L1001" s="32"/>
+      <c r="M1001" s="32"/>
+      <c r="N1001" s="32"/>
+      <c r="O1001" s="32"/>
+      <c r="P1001" s="32"/>
+      <c r="Q1001" s="32"/>
+      <c r="R1001" s="32"/>
+      <c r="S1001" s="32"/>
+      <c r="T1001" s="32"/>
+      <c r="U1001" s="32"/>
+      <c r="V1001" s="32"/>
+      <c r="W1001" s="32"/>
+      <c r="X1001" s="32"/>
+      <c r="Y1001" s="32"/>
+      <c r="Z1001" s="32"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
